--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487747_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487747_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.3489</v>
+        <v>8.451700000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>5.151</v>
+        <v>5.1721</v>
       </c>
       <c r="F2" t="n">
-        <v>3.1979</v>
+        <v>3.2797</v>
       </c>
       <c r="G2" t="n">
         <v>7.4824</v>
@@ -610,13 +610,13 @@
         <v>2.9105</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1036</v>
+        <v>-0.0008</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.12</v>
+        <v>-0.099</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0164</v>
+        <v>0.0982</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>8.182</v>
+        <v>8.0084</v>
       </c>
       <c r="E3" t="n">
-        <v>3.6991</v>
+        <v>3.2802</v>
       </c>
       <c r="F3" t="n">
-        <v>4.4829</v>
+        <v>4.7282</v>
       </c>
       <c r="G3" t="n">
         <v>4.6953</v>
@@ -688,13 +688,13 @@
         <v>2.9105</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5763</v>
+        <v>0.4027</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4262</v>
+        <v>0.0073</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1501</v>
+        <v>0.3954</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.4228</v>
+        <v>4.7776</v>
       </c>
       <c r="E4" t="n">
-        <v>2.6237</v>
+        <v>2.924</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7991</v>
+        <v>1.8536</v>
       </c>
       <c r="G4" t="n">
         <v>7.4751</v>
@@ -766,13 +766,13 @@
         <v>2.3284</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.1895</v>
+        <v>-0.8347</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4845</v>
+        <v>-0.1842</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.705</v>
+        <v>-0.6505</v>
       </c>
       <c r="V4" t="n">
         <v>0.6597</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.968</v>
+        <v>4.2259</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.9651999999999999</v>
+        <v>-0.5438</v>
       </c>
       <c r="F5" t="n">
-        <v>4.9332</v>
+        <v>4.7697</v>
       </c>
       <c r="G5" t="n">
         <v>2.0166</v>
@@ -844,13 +844,13 @@
         <v>2.3284</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5931</v>
+        <v>0.851</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7874</v>
+        <v>-0.3659</v>
       </c>
       <c r="U5" t="n">
-        <v>1.3805</v>
+        <v>1.2169</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.693</v>
+        <v>3.8808</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0437</v>
+        <v>1.2859</v>
       </c>
       <c r="F6" t="n">
-        <v>2.6493</v>
+        <v>2.5948</v>
       </c>
       <c r="G6" t="n">
         <v>2.3877</v>
@@ -922,13 +922,13 @@
         <v>2.7164</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2665</v>
+        <v>0.4542</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4229</v>
+        <v>-0.1806</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6894</v>
+        <v>0.6348</v>
       </c>
       <c r="V6" t="n">
         <v>-0.7075</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.0868</v>
+        <v>2.9687</v>
       </c>
       <c r="E7" t="n">
-        <v>2.3559</v>
+        <v>2.5376</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7309</v>
+        <v>0.4311</v>
       </c>
       <c r="G7" t="n">
         <v>0.8381999999999999</v>
@@ -1000,13 +1000,13 @@
         <v>2.5224</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2739</v>
+        <v>-0.392</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1806</v>
+        <v>0.0011</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.09329999999999999</v>
+        <v>-0.3931</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.8786</v>
+        <v>2.6027</v>
       </c>
       <c r="E8" t="n">
-        <v>1.6544</v>
+        <v>1.5148</v>
       </c>
       <c r="F8" t="n">
-        <v>1.2242</v>
+        <v>1.088</v>
       </c>
       <c r="G8" t="n">
         <v>2.0885</v>
@@ -1078,13 +1078,13 @@
         <v>2.1344</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.092</v>
+        <v>-0.3679</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0617</v>
+        <v>-0.078</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1536</v>
+        <v>-0.2899</v>
       </c>
       <c r="V8" t="n">
         <v>-0.2821</v>
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>2.0613</v>
+        <v>2.0824</v>
       </c>
       <c r="E9" t="n">
-        <v>2.7738</v>
+        <v>2.7948</v>
       </c>
       <c r="F9" t="n">
         <v>-0.7125</v>
@@ -1156,10 +1156,10 @@
         <v>2.1344</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1283</v>
+        <v>-1.1073</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0011</v>
+        <v>0.0221</v>
       </c>
       <c r="U9" t="n">
         <v>-1.1294</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9989</v>
+        <v>-1.7866</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.9156</v>
+        <v>-2.5943</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9167999999999999</v>
+        <v>0.8077</v>
       </c>
       <c r="G10" t="n">
         <v>-0.9919</v>
@@ -1234,13 +1234,13 @@
         <v>1.1642</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2308</v>
+        <v>-0.0185</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4845</v>
+        <v>-0.1632</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2537</v>
+        <v>0.1447</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.4624</v>
+        <v>-2.8201</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.705</v>
+        <v>-2.4442</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7574</v>
+        <v>-0.3758</v>
       </c>
       <c r="G11" t="n">
         <v>0.4626</v>
@@ -1312,13 +1312,13 @@
         <v>1.1642</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0309</v>
+        <v>-0.3886</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6057</v>
+        <v>-0.3449</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4253</v>
+        <v>-0.0437</v>
       </c>
       <c r="V11" t="n">
         <v>-2.1179</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>31.18010000000001</v>
+        <v>32.39149999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>12.7158</v>
+        <v>13.9271</v>
       </c>
       <c r="F12" t="n">
-        <v>18.4644</v>
+        <v>18.4645</v>
       </c>
       <c r="G12" t="n">
         <v>27.8202</v>
@@ -1390,13 +1390,13 @@
         <v>22.3138</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.6131</v>
+        <v>-1.4019</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.5966</v>
+        <v>-1.3853</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.01649999999999979</v>
+        <v>-0.01659999999999993</v>
       </c>
       <c r="V12" t="n">
         <v>-1.7881</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.2476</v>
+        <v>2.6197</v>
       </c>
       <c r="E13" t="n">
-        <v>1.3529</v>
+        <v>0.7523</v>
       </c>
       <c r="F13" t="n">
-        <v>1.8947</v>
+        <v>1.8674</v>
       </c>
       <c r="G13" t="n">
         <v>-0.5223</v>
@@ -1468,13 +1468,13 @@
         <v>0.7761</v>
       </c>
       <c r="S13" t="n">
-        <v>1.1101</v>
+        <v>0.4823</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6684</v>
+        <v>0.0678</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4417</v>
+        <v>0.4144</v>
       </c>
       <c r="V13" t="n">
         <v>1.8836</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. DIAWARA</t>
+          <t>D. ROPERO MORA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.5384</v>
+        <v>-1.0969</v>
       </c>
       <c r="E14" t="n">
-        <v>4.2212</v>
+        <v>-1.0101</v>
       </c>
       <c r="F14" t="n">
-        <v>-4.7596</v>
+        <v>-0.0868</v>
       </c>
       <c r="G14" t="n">
-        <v>-3.4338</v>
+        <v>-1.4821</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.7489</v>
+        <v>-1.4821</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.685</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2.0532</v>
+        <v>-0.6467000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>1.8908</v>
+        <v>-0.6467000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1624</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-5.487</v>
+        <v>-0.8354</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.6397</v>
+        <v>-0.8354</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.8473</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>0.5821</v>
+        <v>0.7761</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5523</v>
+        <v>0.7761</v>
       </c>
       <c r="S14" t="n">
-        <v>2.973</v>
+        <v>-0.3909</v>
       </c>
       <c r="T14" t="n">
-        <v>2.574</v>
+        <v>-0.3634</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3991</v>
+        <v>-0.0275</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.6597</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5642</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. ROPERO MORA</t>
+          <t>M. DIAWARA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.1241</v>
+        <v>-2.3036</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.0101</v>
+        <v>2.6196</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.114</v>
+        <v>-4.9231</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.4821</v>
+        <v>-3.4338</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.4821</v>
+        <v>-0.7489</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>-2.685</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.6467000000000001</v>
+        <v>2.0532</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.6467000000000001</v>
+        <v>1.8908</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>0.1624</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.8354</v>
+        <v>-5.487</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8354</v>
+        <v>-2.6397</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>-2.8473</v>
       </c>
       <c r="P15" t="n">
-        <v>0.7761</v>
+        <v>0.5821</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R15" t="n">
-        <v>0.7761</v>
+        <v>1.5523</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4181</v>
+        <v>1.2079</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3634</v>
+        <v>0.9724</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0547</v>
+        <v>0.2355</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-0.6597</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.5642</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.7149</v>
+        <v>-3.0791</v>
       </c>
       <c r="E16" t="n">
-        <v>0.523</v>
+        <v>0.0225</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.2379</v>
+        <v>-3.1016</v>
       </c>
       <c r="G16" t="n">
         <v>-4.8456</v>
@@ -1702,13 +1702,13 @@
         <v>2.1344</v>
       </c>
       <c r="S16" t="n">
-        <v>1.2202</v>
+        <v>0.856</v>
       </c>
       <c r="T16" t="n">
-        <v>1.2393</v>
+        <v>0.7388</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0191</v>
+        <v>0.1172</v>
       </c>
       <c r="V16" t="n">
         <v>-1.2239</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>F. ESPINOSA</t>
+          <t>D. PETIT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.9759</v>
+        <v>-3.0793</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.6594</v>
+        <v>-3.352</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6835</v>
+        <v>0.2728</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.1628</v>
+        <v>-2.7663</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.3167</v>
+        <v>-1.8092</v>
       </c>
       <c r="I17" t="n">
-        <v>1.154</v>
+        <v>-0.9571</v>
       </c>
       <c r="J17" t="n">
-        <v>1.5829</v>
+        <v>-1.2788</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.2719</v>
+        <v>-0.0659</v>
       </c>
       <c r="L17" t="n">
-        <v>1.8547</v>
+        <v>-1.2129</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.7456</v>
+        <v>-1.4875</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.0449</v>
+        <v>-1.7433</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7008</v>
+        <v>0.2558</v>
       </c>
       <c r="P17" t="n">
-        <v>-3.4926</v>
+        <v>-1.1642</v>
       </c>
       <c r="Q17" t="n">
-        <v>-5.821</v>
+        <v>-2.9105</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3284</v>
+        <v>1.7463</v>
       </c>
       <c r="S17" t="n">
-        <v>1.1153</v>
+        <v>-0.3726</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0145</v>
+        <v>-0.6688</v>
       </c>
       <c r="U17" t="n">
-        <v>1.1008</v>
+        <v>0.2961</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5642</v>
+        <v>1.2239</v>
       </c>
       <c r="W17" t="n">
-        <v>0.5642</v>
+        <v>1.506</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. PETIT</t>
+          <t>S. KIMOTO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.325</v>
+        <v>-3.2227</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.6523</v>
+        <v>-0.5409</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3273</v>
+        <v>-2.6818</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.7663</v>
+        <v>-2.2409</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.8092</v>
+        <v>-0.9127999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.9571</v>
+        <v>-1.328</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.2788</v>
+        <v>1.6769</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.0659</v>
+        <v>0.964</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.2129</v>
+        <v>0.713</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.4875</v>
+        <v>-3.9178</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.7433</v>
+        <v>-1.8768</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2558</v>
+        <v>-2.041</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.1642</v>
+        <v>-2.9105</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.9105</v>
+        <v>-3.8806</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7463</v>
+        <v>0.9702</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6183999999999999</v>
+        <v>0.7526</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9691</v>
+        <v>0.4867</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3506</v>
+        <v>0.2658</v>
       </c>
       <c r="V18" t="n">
-        <v>1.2239</v>
+        <v>1.1761</v>
       </c>
       <c r="W18" t="n">
-        <v>1.506</v>
+        <v>1.1761</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2821</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. KIMOTO</t>
+          <t>F. ESPINOSA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.6231</v>
+        <v>-3.3664</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9413</v>
+        <v>-3.5593</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.6818</v>
+        <v>0.1929</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.2409</v>
+        <v>-1.1628</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.9127999999999999</v>
+        <v>-2.3167</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.328</v>
+        <v>1.154</v>
       </c>
       <c r="J19" t="n">
-        <v>1.6769</v>
+        <v>1.5829</v>
       </c>
       <c r="K19" t="n">
-        <v>0.964</v>
+        <v>-0.2719</v>
       </c>
       <c r="L19" t="n">
-        <v>0.713</v>
+        <v>1.8547</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.9178</v>
+        <v>-2.7456</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.8768</v>
+        <v>-2.0449</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.041</v>
+        <v>-0.7008</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.9105</v>
+        <v>-3.4926</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.8806</v>
+        <v>-5.821</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9702</v>
+        <v>2.3284</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3522</v>
+        <v>0.7248</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0863</v>
+        <v>0.1146</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2658</v>
+        <v>0.6102</v>
       </c>
       <c r="V19" t="n">
-        <v>1.1761</v>
+        <v>0.5642</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1761</v>
+        <v>0.5642</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. CARABALLO ROPERO</t>
+          <t>P. BARCALA BELTRAN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.9268</v>
+        <v>-4.3377</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.8474</v>
+        <v>-3.1839</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.0794</v>
+        <v>-1.1539</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.5599</v>
+        <v>-2.1403</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.3686</v>
+        <v>-3.9265</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1913</v>
+        <v>1.7863</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.1505</v>
+        <v>0.5042</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5643</v>
+        <v>-2.6446</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5861</v>
+        <v>3.1488</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.4095</v>
+        <v>-2.6445</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.8043</v>
+        <v>-1.282</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3948</v>
+        <v>-1.3625</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.194</v>
+        <v>-1.3582</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9702</v>
+        <v>-2.9105</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7761</v>
+        <v>1.5523</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6669</v>
+        <v>-0.5572</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7268</v>
+        <v>-0.7776</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0599</v>
+        <v>0.2204</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.506</v>
+        <v>-0.2821</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.506</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. BARCALA BELTRAN</t>
+          <t>D. CARABALLO ROPERO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.9378</v>
+        <v>-4.572</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.4842</v>
+        <v>-2.5471</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4537</v>
+        <v>-2.0249</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.1403</v>
+        <v>-2.5599</v>
       </c>
       <c r="H21" t="n">
-        <v>-3.9265</v>
+        <v>-2.3686</v>
       </c>
       <c r="I21" t="n">
-        <v>1.7863</v>
+        <v>-0.1913</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5042</v>
+        <v>-1.1505</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.6446</v>
+        <v>-0.5643</v>
       </c>
       <c r="L21" t="n">
-        <v>3.1488</v>
+        <v>-0.5861</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.6445</v>
+        <v>-1.4095</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.282</v>
+        <v>-1.8043</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.3625</v>
+        <v>0.3948</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.3582</v>
+        <v>-0.194</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.9105</v>
+        <v>-0.9702</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5523</v>
+        <v>0.7761</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1573</v>
+        <v>-0.3121</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0779</v>
+        <v>-0.4265</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0794</v>
+        <v>0.1144</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.2821</v>
+        <v>-1.506</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2821</v>
+        <v>-1.506</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-10.2615</v>
+        <v>-8.7422</v>
       </c>
       <c r="E22" t="n">
-        <v>-8.9666</v>
+        <v>-7.6654</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.2949</v>
+        <v>-1.0769</v>
       </c>
       <c r="G22" t="n">
         <v>-6.666</v>
@@ -2170,13 +2170,13 @@
         <v>1.9403</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.297</v>
+        <v>0.2223</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.4289</v>
+        <v>-0.1276</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1319</v>
+        <v>0.35</v>
       </c>
       <c r="V22" t="n">
         <v>0.6119</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-31.1799</v>
+        <v>-31.1802</v>
       </c>
       <c r="E23" t="n">
-        <v>-18.4642</v>
+        <v>-18.4643</v>
       </c>
       <c r="F23" t="n">
-        <v>-12.7158</v>
+        <v>-12.7159</v>
       </c>
       <c r="G23" t="n">
         <v>-27.82</v>
@@ -2218,7 +2218,7 @@
         <v>-21.0908</v>
       </c>
       <c r="I23" t="n">
-        <v>-6.728999999999999</v>
+        <v>-6.729</v>
       </c>
       <c r="J23" t="n">
         <v>-1.7656</v>
@@ -2227,7 +2227,7 @@
         <v>-3.9625</v>
       </c>
       <c r="L23" t="n">
-        <v>2.197</v>
+        <v>2.196999999999999</v>
       </c>
       <c r="M23" t="n">
         <v>-26.0544</v>
@@ -2251,10 +2251,10 @@
         <v>2.6131</v>
       </c>
       <c r="T23" t="n">
-        <v>0.01639999999999953</v>
+        <v>0.01640000000000014</v>
       </c>
       <c r="U23" t="n">
-        <v>2.5966</v>
+        <v>2.5965</v>
       </c>
       <c r="V23" t="n">
         <v>1.788</v>
